--- a/docs/files/REPORT_FILTRI/CR - DE LUCA ANTONIO.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - DE LUCA ANTONIO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>7</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1374</v>
+        <v>1839</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1125</v>
+        <v>1513</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>357</v>
+        <v>493</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>778</v>
+        <v>1030</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>685</v>
+        <v>941</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>175</v>
+        <v>233</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>183</v>
+        <v>303</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>677</v>
+        <v>901</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>305</v>
+        <v>397</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>342</v>
+        <v>438</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>402</v>
+        <v>519</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>389</v>
+        <v>527</v>
       </c>
       <c r="G12" s="12" t="n">
+        <v>196</v>
+      </c>
+      <c r="H12" s="12" t="n">
+        <v>372</v>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>396</v>
+      </c>
+      <c r="J12" s="12" t="n">
         <v>150</v>
       </c>
-      <c r="H12" s="12" t="n">
-        <v>273</v>
-      </c>
-      <c r="I12" s="12" t="n">
-        <v>301</v>
-      </c>
-      <c r="J12" s="12" t="n">
-        <v>116</v>
-      </c>
       <c r="K12" s="12" t="n">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>354</v>
+        <v>458</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>166</v>
+        <v>235</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>146</v>
+        <v>208</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1033,31 +1033,31 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1087,35 +1087,35 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1141,35 +1141,35 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>4</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J17" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/CR - DE LUCA ANTONIO.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - DE LUCA ANTONIO.xlsx
@@ -535,7 +535,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -845,7 +845,7 @@
         <v>438</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.0593607305936073</v>
+        <v>26</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>458</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.2620087336244541</v>
+        <v>120</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>208</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.09615384615384616</v>
+        <v>20</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>126</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.4444444444444444</v>
+        <v>56</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         <v>63</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>0.01587301587301587</v>
+        <v>1</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>72</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.25</v>
+        <v>18</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>47</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.0851063829787234</v>
+        <v>4</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/CR - DE LUCA ANTONIO.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - DE LUCA ANTONIO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>7</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1839</v>
+        <v>1939</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1513</v>
+        <v>1599</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>493</v>
+        <v>537</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,28 +821,28 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>1030</v>
+        <v>1080</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>941</v>
+        <v>1004</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>303</v>
+        <v>333</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>901</v>
+        <v>947</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>397</v>
+        <v>418</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>26</v>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>519</v>
+        <v>546</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>527</v>
+        <v>562</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>372</v>
+        <v>401</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>396</v>
+        <v>417</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>458</v>
+        <v>484</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,28 +929,28 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>34</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>20</v>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1033,28 +1033,28 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="J15" s="12" t="n">
         <v>11</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>1</v>
@@ -1087,31 +1087,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J16" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/CR - DE LUCA ANTONIO.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - DE LUCA ANTONIO.xlsx
@@ -1026,7 +1026,11 @@
           <t>MONSUMMANO TERME</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
           <t>DE LUCA ANTONIO</t>

--- a/docs/files/REPORT_FILTRI/CR - DE LUCA ANTONIO.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - DE LUCA ANTONIO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>7</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1939</v>
+        <v>2055</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1599</v>
+        <v>1695</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>537</v>
+        <v>586</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>1080</v>
+        <v>1126</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1004</v>
+        <v>1062</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>333</v>
+        <v>361</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>947</v>
+        <v>988</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>458</v>
+        <v>479</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>546</v>
+        <v>574</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>562</v>
+        <v>590</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>417</v>
+        <v>440</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>484</v>
+        <v>503</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>121</v>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J14" s="12" t="n">
         <v>27</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,28 +1037,28 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>1</v>
@@ -1091,28 +1091,28 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J16" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>19</v>
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>4</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J17" s="12" t="n">
         <v>3</v>
@@ -1166,10 +1166,10 @@
         <v>11</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/CR - DE LUCA ANTONIO.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - DE LUCA ANTONIO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>7</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2055</v>
+        <v>2187</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1695</v>
+        <v>1814</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>586</v>
+        <v>641</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>1126</v>
+        <v>1177</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1062</v>
+        <v>1167</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>263</v>
+        <v>282</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>361</v>
+        <v>408</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>988</v>
+        <v>1037</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>436</v>
+        <v>455</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>479</v>
+        <v>512</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,35 +875,35 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>574</v>
+        <v>606</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>590</v>
+        <v>639</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>440</v>
+        <v>466</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>503</v>
+        <v>535</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -929,28 +929,28 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>22</v>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J14" s="12" t="n">
         <v>27</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,28 +1037,28 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>1</v>
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>2</v>
@@ -1103,19 +1103,19 @@
         <v>11</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J16" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>4</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>14</v>
@@ -1163,13 +1163,13 @@
         <v>3</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/CR - DE LUCA ANTONIO.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - DE LUCA ANTONIO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>7</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2187</v>
+        <v>2345</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1814</v>
+        <v>1947</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>641</v>
+        <v>712</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>1177</v>
+        <v>1251</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1167</v>
+        <v>1245</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>282</v>
+        <v>311</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>408</v>
+        <v>440</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>1037</v>
+        <v>1105</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>455</v>
+        <v>486</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>512</v>
+        <v>544</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,35 +875,35 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>606</v>
+        <v>651</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>639</v>
+        <v>661</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>433</v>
+        <v>455</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>466</v>
+        <v>497</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>535</v>
+        <v>567</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -929,28 +929,28 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>39</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>22</v>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,35 +1037,35 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J17" s="12" t="n">
         <v>3</v>
@@ -1166,10 +1166,10 @@
         <v>12</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/CR - DE LUCA ANTONIO.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - DE LUCA ANTONIO.xlsx
@@ -810,11 +810,7 @@
           <t>PRATO</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Tino Vincenzo</t>
-        </is>
-      </c>
+      <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
           <t>DE LUCA ANTONIO</t>

--- a/docs/files/REPORT_FILTRI/CR - DE LUCA ANTONIO.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - DE LUCA ANTONIO.xlsx
@@ -209,23 +209,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N17" headerRowCount="1">
-  <autoFilter ref="A10:N17"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O17" headerRowCount="1">
+  <autoFilter ref="A10:O17"/>
+  <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
-    <tableColumn id="3" name="Agente"/>
-    <tableColumn id="4" name="CR"/>
-    <tableColumn id="5" name="Vend 2026"/>
-    <tableColumn id="6" name="Vend 2025"/>
-    <tableColumn id="7" name="Ass 2026"/>
-    <tableColumn id="8" name="Ass 2025"/>
-    <tableColumn id="9" name="Prospect"/>
-    <tableColumn id="10" name="Twin"/>
-    <tableColumn id="11" name="Business"/>
-    <tableColumn id="12" name="Sost anno"/>
-    <tableColumn id="13" name="UP EU"/>
-    <tableColumn id="14" name="Stato"/>
+    <tableColumn id="3" name="Indirizzo"/>
+    <tableColumn id="4" name="Agente"/>
+    <tableColumn id="5" name="CR"/>
+    <tableColumn id="6" name="Vend 2026"/>
+    <tableColumn id="7" name="Vend 2025"/>
+    <tableColumn id="8" name="Ass 2026"/>
+    <tableColumn id="9" name="Ass 2025"/>
+    <tableColumn id="10" name="Prospect"/>
+    <tableColumn id="11" name="Twin"/>
+    <tableColumn id="12" name="Business"/>
+    <tableColumn id="13" name="Sost anno"/>
+    <tableColumn id="14" name="UP EU"/>
+    <tableColumn id="15" name="Stato"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -520,23 +521,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -558,6 +560,7 @@
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="2" t="n"/>
       <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -574,6 +577,7 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -598,6 +602,7 @@
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -622,6 +627,7 @@
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -638,6 +644,7 @@
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -670,6 +677,7 @@
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -694,6 +702,7 @@
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -710,6 +719,7 @@
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -726,6 +736,7 @@
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -740,60 +751,65 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
+          <t>Indirizzo</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Vend 2026</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Vend 2025</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Ass 2026</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Ass 2025</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>Twin</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Sost anno</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>UP EU</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
@@ -810,40 +826,45 @@
           <t>PRATO</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>VIALE NAM DINH  N 4 - LATO OVEST</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>DE LUCA ANTONIO</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>1251</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>1245</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="H11" s="12" t="n">
         <v>311</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="I11" s="12" t="n">
         <v>440</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="J11" s="12" t="n">
         <v>1105</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="K11" s="12" t="n">
         <v>486</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="L11" s="12" t="n">
         <v>122</v>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="M11" s="12" t="n">
         <v>544</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="N11" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -862,42 +883,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>R.A. FI-MARE / VIA NICCOLO' MACCHIAVELLI 287</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>DE LUCA ANTONIO</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>651</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>661</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="H12" s="12" t="n">
         <v>258</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="I12" s="12" t="n">
         <v>455</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="J12" s="12" t="n">
         <v>497</v>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="K12" s="12" t="n">
         <v>187</v>
       </c>
-      <c r="K12" s="12" t="n">
+      <c r="L12" s="12" t="n">
         <v>144</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="M12" s="12" t="n">
         <v>567</v>
       </c>
-      <c r="M12" s="12" t="n">
+      <c r="N12" s="12" t="n">
         <v>123</v>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -916,42 +942,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>MACALLE', 26</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>DE LUCA ANTONIO</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>177</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>286</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="H13" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="I13" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="J13" s="12" t="n">
         <v>135</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="K13" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="K13" s="12" t="n">
+      <c r="L13" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="L13" s="12" t="n">
+      <c r="M13" s="12" t="n">
         <v>258</v>
       </c>
-      <c r="M13" s="12" t="n">
+      <c r="N13" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -970,42 +1001,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>XVI APRILE</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>DE LUCA ANTONIO</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="H14" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="I14" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="J14" s="12" t="n">
         <v>79</v>
       </c>
-      <c r="J14" s="12" t="n">
+      <c r="K14" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="K14" s="12" t="n">
+      <c r="L14" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="L14" s="12" t="n">
+      <c r="M14" s="12" t="n">
         <v>158</v>
       </c>
-      <c r="M14" s="12" t="n">
+      <c r="N14" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1024,42 +1060,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>DELLA COSTITUZIONE, 138</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>DE LUCA ANTONIO</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="H15" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="I15" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="12" t="n">
+      <c r="J15" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="K15" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="K15" s="12" t="n">
+      <c r="L15" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L15" s="12" t="n">
+      <c r="M15" s="12" t="n">
         <v>101</v>
       </c>
-      <c r="M15" s="12" t="n">
+      <c r="N15" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1078,42 +1119,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>S.G.C. FIPILI KM 52,800 - LOC. CURIGLIANO</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>DE LUCA ANTONIO</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="H16" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="I16" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="J16" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="K16" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="L16" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="L16" s="12" t="n">
+      <c r="M16" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="M16" s="12" t="n">
+      <c r="N16" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1132,42 +1178,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>S.G.C. FI/PI/LI LOC.GRECCIANO SUD 64</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>DE LUCA ANTONIO</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="H17" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H17" s="12" t="n">
+      <c r="I17" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="I17" s="12" t="n">
+      <c r="J17" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="K17" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K17" s="12" t="n">
+      <c r="L17" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L17" s="12" t="n">
+      <c r="M17" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="M17" s="12" t="n">
+      <c r="N17" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>

--- a/docs/files/REPORT_FILTRI/CR - DE LUCA ANTONIO.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - DE LUCA ANTONIO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>7</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2345</v>
+        <v>2459</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1947</v>
+        <v>2041</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>712</v>
+        <v>761</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -838,31 +838,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1251</v>
+        <v>1320</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1245</v>
+        <v>1329</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>311</v>
+        <v>338</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>440</v>
+        <v>491</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>1105</v>
+        <v>1168</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>486</v>
+        <v>520</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>544</v>
+        <v>575</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -897,31 +897,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>651</v>
+        <v>681</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>661</v>
+        <v>707</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>455</v>
+        <v>494</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>497</v>
+        <v>516</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>567</v>
+        <v>597</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>39</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>22</v>
@@ -1015,28 +1015,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>62</v>
@@ -1074,28 +1074,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>1</v>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>3</v>
@@ -1151,13 +1151,13 @@
         <v>5</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1192,19 +1192,19 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>29</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>3</v>
@@ -1213,10 +1213,10 @@
         <v>12</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/CR - DE LUCA ANTONIO.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - DE LUCA ANTONIO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>7</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2459</v>
+        <v>2579</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2041</v>
+        <v>2147</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>761</v>
+        <v>809</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -838,28 +838,28 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1320</v>
+        <v>1383</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1329</v>
+        <v>1447</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>338</v>
+        <v>368</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>491</v>
+        <v>552</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>1168</v>
+        <v>1228</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>520</v>
+        <v>550</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>575</v>
+        <v>616</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>31</v>
@@ -897,35 +897,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>681</v>
+        <v>720</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>707</v>
+        <v>765</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>494</v>
+        <v>545</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>516</v>
+        <v>546</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>597</v>
+        <v>632</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>273</v>
+        <v>301</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1015,28 +1015,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>18</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>62</v>
@@ -1074,10 +1074,10 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>59</v>
@@ -1086,16 +1086,16 @@
         <v>0</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>1</v>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>3</v>
@@ -1145,19 +1145,19 @@
         <v>13</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1192,31 +1192,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>29</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/CR - DE LUCA ANTONIO.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - DE LUCA ANTONIO.xlsx
@@ -538,7 +538,7 @@
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>7</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2579</v>
+        <v>2720</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2147</v>
+        <v>2268</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>809</v>
+        <v>873</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -838,35 +838,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1383</v>
+        <v>1470</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1447</v>
+        <v>1602</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>368</v>
+        <v>408</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>552</v>
+        <v>633</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>1228</v>
+        <v>1308</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>550</v>
+        <v>589</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>616</v>
+        <v>656</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -897,31 +897,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>720</v>
+        <v>752</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>765</v>
+        <v>845</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>545</v>
+        <v>591</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>546</v>
+        <v>567</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>632</v>
+        <v>664</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>40</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>301</v>
+        <v>331</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>25</v>
@@ -1015,28 +1015,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>62</v>
@@ -1074,35 +1074,35 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G15" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1133,19 +1133,19 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>5</v>
@@ -1154,10 +1154,10 @@
         <v>30</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>8</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J17" s="12" t="n">
         <v>18</v>
@@ -1213,10 +1213,10 @@
         <v>12</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/CR - DE LUCA ANTONIO.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - DE LUCA ANTONIO.xlsx
@@ -538,7 +538,7 @@
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>7</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2720</v>
+        <v>2869</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2268</v>
+        <v>2392</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>873</v>
+        <v>930</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -838,31 +838,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1470</v>
+        <v>1581</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1602</v>
+        <v>1675</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>408</v>
+        <v>450</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>633</v>
+        <v>670</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>1308</v>
+        <v>1397</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>589</v>
+        <v>637</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>656</v>
+        <v>693</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -897,31 +897,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>752</v>
+        <v>775</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>845</v>
+        <v>886</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>591</v>
+        <v>622</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>567</v>
+        <v>590</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>174</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>664</v>
+        <v>705</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>40</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>331</v>
+        <v>353</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1015,31 +1015,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1074,19 +1074,19 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>25</v>
@@ -1095,14 +1095,14 @@
         <v>6</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>3</v>
@@ -1145,7 +1145,7 @@
         <v>14</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>5</v>
@@ -1154,7 +1154,7 @@
         <v>30</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>27</v>
@@ -1192,31 +1192,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/CR - DE LUCA ANTONIO.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - DE LUCA ANTONIO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>7</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2869</v>
+        <v>3024</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2392</v>
+        <v>2530</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>930</v>
+        <v>999</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -838,35 +838,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1581</v>
+        <v>1675</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1675</v>
+        <v>1749</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>450</v>
+        <v>488</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>670</v>
+        <v>707</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>1397</v>
+        <v>1485</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>637</v>
+        <v>684</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>693</v>
+        <v>727</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>36</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -897,28 +897,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>775</v>
+        <v>815</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>886</v>
+        <v>941</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>313</v>
+        <v>336</v>
       </c>
       <c r="I12" s="12" t="n">
+        <v>663</v>
+      </c>
+      <c r="J12" s="12" t="n">
         <v>622</v>
       </c>
-      <c r="J12" s="12" t="n">
-        <v>590</v>
-      </c>
       <c r="K12" s="12" t="n">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>705</v>
+        <v>739</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>128</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>64</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>40</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>353</v>
+        <v>378</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>26</v>
@@ -1015,28 +1015,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>67</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>61</v>
@@ -1095,7 +1095,7 @@
         <v>6</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>1</v>
@@ -1133,31 +1133,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>14</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>9</v>
@@ -1204,19 +1204,19 @@
         <v>31</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/CR - DE LUCA ANTONIO.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - DE LUCA ANTONIO.xlsx
@@ -538,7 +538,7 @@
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>7</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3024</v>
+        <v>3147</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2530</v>
+        <v>2628</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>999</v>
+        <v>1063</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -838,35 +838,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1675</v>
+        <v>1722</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1749</v>
+        <v>1823</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>488</v>
+        <v>509</v>
       </c>
       <c r="I11" s="12" t="n">
+        <v>745</v>
+      </c>
+      <c r="J11" s="12" t="n">
+        <v>1530</v>
+      </c>
+      <c r="K11" s="12" t="n">
         <v>707</v>
       </c>
-      <c r="J11" s="12" t="n">
-        <v>1485</v>
-      </c>
-      <c r="K11" s="12" t="n">
-        <v>684</v>
-      </c>
       <c r="L11" s="12" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>727</v>
+        <v>773</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -897,28 +897,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>815</v>
+        <v>859</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>941</v>
+        <v>983</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>336</v>
+        <v>363</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>663</v>
+        <v>695</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>622</v>
+        <v>652</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>739</v>
+        <v>780</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>128</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>64</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>378</v>
+        <v>406</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1015,28 +1015,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>61</v>
@@ -1074,35 +1074,35 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G15" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1133,31 +1133,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>14</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1195,13 +1195,13 @@
         <v>33</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J17" s="12" t="n">
         <v>20</v>
@@ -1213,7 +1213,7 @@
         <v>13</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>17</v>

--- a/docs/files/REPORT_FILTRI/CR - DE LUCA ANTONIO.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - DE LUCA ANTONIO.xlsx
@@ -538,7 +538,7 @@
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>7</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3147</v>
+        <v>3355</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2628</v>
+        <v>2818</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1063</v>
+        <v>1181</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -838,35 +838,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1722</v>
+        <v>1827</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1823</v>
+        <v>1886</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>509</v>
+        <v>555</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>745</v>
+        <v>786</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>1530</v>
+        <v>1625</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>707</v>
+        <v>757</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>773</v>
+        <v>815</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -897,31 +897,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>859</v>
+        <v>931</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>983</v>
+        <v>1032</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>363</v>
+        <v>416</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>695</v>
+        <v>733</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>652</v>
+        <v>717</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>259</v>
+        <v>292</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>780</v>
+        <v>841</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>41</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>406</v>
+        <v>429</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1015,31 +1015,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>26</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1074,28 +1074,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="G15" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="I15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>7</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>1</v>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>6</v>
@@ -1145,16 +1145,16 @@
         <v>14</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>7</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>34</v>
@@ -1195,10 +1195,10 @@
         <v>33</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>32</v>
@@ -1213,10 +1213,10 @@
         <v>13</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/CR - DE LUCA ANTONIO.xlsx
+++ b/docs/files/REPORT_FILTRI/CR - DE LUCA ANTONIO.xlsx
@@ -538,7 +538,7 @@
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -684,13 +684,13 @@
         <v>7</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3355</v>
+        <v>3322</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2818</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1181</v>
+        <v>1166</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -838,19 +838,19 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1827</v>
+        <v>1804</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1886</v>
+        <v>1847</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>555</v>
+        <v>545</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>786</v>
+        <v>779</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>1625</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>757</v>
@@ -859,14 +859,14 @@
         <v>179</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>815</v>
+        <v>801</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -897,19 +897,19 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>931</v>
+        <v>920</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>1032</v>
+        <v>1017</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>733</v>
+        <v>724</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>717</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>292</v>
@@ -918,7 +918,7 @@
         <v>203</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>841</v>
+        <v>831</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>144</v>
@@ -956,19 +956,19 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>72</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>194</v>
+        <v>0</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>100</v>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>145</v>
@@ -1027,7 +1027,7 @@
         <v>73</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>50</v>
@@ -1036,10 +1036,10 @@
         <v>26</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1074,10 +1074,10 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>73</v>
@@ -1086,7 +1086,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>31</v>
@@ -1136,16 +1136,16 @@
         <v>75</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>6</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>7</v>
@@ -1154,10 +1154,10 @@
         <v>35</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1195,16 +1195,16 @@
         <v>33</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>11</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>6</v>
@@ -1213,7 +1213,7 @@
         <v>13</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>19</v>
